--- a/artfynd/A 1863-2022 artfynd.xlsx
+++ b/artfynd/A 1863-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960875</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956721</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963496</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960028</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955277</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964123</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968844</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956719</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,8 +1591,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964546</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 1863-2022 artfynd.xlsx
+++ b/artfynd/A 1863-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134960875</v>
       </c>
       <c r="B2" t="n">
-        <v>80344</v>
+        <v>80382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>134956721</v>
       </c>
       <c r="B3" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>134963496</v>
       </c>
       <c r="B4" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>134960028</v>
       </c>
       <c r="B5" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>134955277</v>
       </c>
       <c r="B6" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>134964123</v>
       </c>
       <c r="B7" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>134968844</v>
       </c>
       <c r="B8" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>134956719</v>
       </c>
       <c r="B9" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134964546</v>
       </c>
       <c r="B10" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
